--- a/listening/ielts_synonym_bank.xlsx
+++ b/listening/ielts_synonym_bank.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,24 @@
       <color rgb="004472C4"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +88,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +128,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2786,48 +2814,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>题目原词</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>音频用词</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>出处</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>★重点</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>已掌握</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>approximately</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>about</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>C14T1S1 Q4</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>I'm actually Canadian</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>C14T1S1 Q1</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>current address</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>where you're staying now</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>C14T1S1 Q3</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>ask lots of questions</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>check with someone if you're not sure</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>C14T1S2 Q12</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>making career plans</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>discuss your long-term ambitions</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>C14T1S2 Q13</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>against the rules</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>we ask that you don't book any</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>C14T1S2 Q17</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>encouraged</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>preferable / we advise you to take it up</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>C14T1S2 Q18-19</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>maximum group size</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>up to fifteen</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>C4T1S1 Q2</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>included in the price</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>no extra charge / part of the accommodation package</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>C4T1S1 Q5-6</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>(price correction)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>usually $300... oh, it's actually $280</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>C4T1S1 Q7</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>under (age)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>below ... years of age</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>C6T2S1 Q1</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>reduced in number</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>fewer</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q13</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>doubled in number</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>twice as many</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q14</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>increased in size</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>converted into two large rooms</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q16</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>replaced</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>they've now gone, and we've got new ones</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q15</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>temporarily closed</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>isn't yet complete / reopen in the next few months</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q12</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>given separate entrance</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>its own access from the side</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q11</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>suitable for</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>which were suitable for</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q14</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>meet demand</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>hope will meet demand</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>C6T1S2 Q14</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
